--- a/output/法令更新監視台帳_20260317.xlsx
+++ b/output/法令更新監視台帳_20260317.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="98">
   <si>
     <t>法令名</t>
   </si>
@@ -58,30 +58,69 @@
     <t>騒音規制法</t>
   </si>
   <si>
+    <t>騒音規制法施行令</t>
+  </si>
+  <si>
+    <t>騒音規制法施行規則</t>
+  </si>
+  <si>
     <t>振動規制法</t>
   </si>
   <si>
+    <t>振動規制法施行令</t>
+  </si>
+  <si>
+    <t>振動規制法施行規則</t>
+  </si>
+  <si>
     <t>悪臭防止法</t>
   </si>
   <si>
     <t>廃棄物の処理及び清掃に関する法律</t>
   </si>
   <si>
-    <t>海洋汚染等及び海上災害の防止に関する法律</t>
+    <t>廃棄物の処理及び清掃に関する法律施行令</t>
+  </si>
+  <si>
+    <t>廃棄物の処理及び清掃に関する法律施行規則</t>
   </si>
   <si>
     <t>下水道法</t>
   </si>
   <si>
+    <t>浄化槽法</t>
+  </si>
+  <si>
+    <t>環境基本法</t>
+  </si>
+  <si>
+    <t>災害対策基本法</t>
+  </si>
+  <si>
+    <t>災害対策基本法施行令</t>
+  </si>
+  <si>
+    <t>災害対策基本法施行規則</t>
+  </si>
+  <si>
     <t>化学物質の審査及び製造等の規制に関する法律</t>
   </si>
   <si>
     <t>特定化学物質の環境への排出量の把握等及び管理の改善の促進に関する法律</t>
   </si>
   <si>
+    <t>特定化学物質の環境への排出量の把握等及び管理の改善の促進に関する法律施行令</t>
+  </si>
+  <si>
     <t>消防法</t>
   </si>
   <si>
+    <t>消防法施行令</t>
+  </si>
+  <si>
+    <t>消防法施行規則</t>
+  </si>
+  <si>
     <t>外国為替及び外国貿易法</t>
   </si>
   <si>
@@ -91,7 +130,13 @@
     <t>地球温暖化対策の推進に関する法律</t>
   </si>
   <si>
-    <t>建築物のエネルギー消費性能向上等に関する法律</t>
+    <t>建築物のエネルギー消費性能の向上等に関する法律</t>
+  </si>
+  <si>
+    <t>建築物のエネルギー消費性能の向上等に関する法律施行令</t>
+  </si>
+  <si>
+    <t>建築物のエネルギー消費性能の向上等に関する法律施行規則</t>
   </si>
   <si>
     <t>フロン類の使用の合理化及び管理の適正化に関する法律</t>
@@ -136,6 +181,15 @@
     <t>労働安全衛生規則</t>
   </si>
   <si>
+    <t>特定工場における公害防止組織の整備に関する法律</t>
+  </si>
+  <si>
+    <t>特定工場における公害防止組織の整備に関する法律施行令</t>
+  </si>
+  <si>
+    <t>特定工場における公害防止組織の整備に関する法律施行規則</t>
+  </si>
+  <si>
     <t>令和四年六月一七日法律第六八号</t>
   </si>
   <si>
@@ -154,7 +208,31 @@
     <t>令和五年一〇月一八日政令第三〇四号</t>
   </si>
   <si>
-    <t>令和六年五月二四日法律第三八号</t>
+    <t>令和三年一二月二四日政令第三四六号</t>
+  </si>
+  <si>
+    <t>令和三年三月二五日環境省令第三号</t>
+  </si>
+  <si>
+    <t>令和五年一二月一日政令第三四四号</t>
+  </si>
+  <si>
+    <t>令和七年一一月一二日環境省令第二二号</t>
+  </si>
+  <si>
+    <t>令和五年六月一六日法律第五八号</t>
+  </si>
+  <si>
+    <t>令和三年五月一九日法律第三六号</t>
+  </si>
+  <si>
+    <t>令和七年六月四日法律第五一号</t>
+  </si>
+  <si>
+    <t>令和七年六月六日政令第二〇七号</t>
+  </si>
+  <si>
+    <t>令和八年二月二〇日内閣府令第四号</t>
   </si>
   <si>
     <t>令和五年一二月一三日法律第八四号</t>
@@ -163,7 +241,13 @@
     <t>平成一四年一二月一三日法律第一五二号</t>
   </si>
   <si>
-    <t>令和五年六月一六日法律第五八号</t>
+    <t>令和六年三月二九日政令第一〇二号</t>
+  </si>
+  <si>
+    <t>令和七年三月二六日政令第八五号</t>
+  </si>
+  <si>
+    <t>令和七年一〇月一日総務省令第九九号</t>
   </si>
   <si>
     <t>令和四年一二月九日法律第九七号</t>
@@ -172,7 +256,13 @@
     <t>令和六年六月一九日法律第五六号</t>
   </si>
   <si>
-    <t>取得失敗（名称不一致）</t>
+    <t>令和六年六月一九日法律第五三号</t>
+  </si>
+  <si>
+    <t>令和六年四月一九日政令第一七二号</t>
+  </si>
+  <si>
+    <t>令和六年一二月二七日国土交通省令第一一一号</t>
   </si>
   <si>
     <t>平成二九年六月一六日法律第六一号</t>
@@ -211,10 +301,10 @@
     <t>令和七年一一月一八日厚生労働省令第一一三号</t>
   </si>
   <si>
+    <t>令和二年一二月二八日財務省・厚生労働省・農林水産省・経済産業省・国土交通省・環境省令第二号</t>
+  </si>
+  <si>
     <t>未確認</t>
-  </si>
-  <si>
-    <t>要確認</t>
   </si>
   <si>
     <t>2026-03-17</t>
@@ -575,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -597,13 +687,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -611,13 +701,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -625,13 +715,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -639,13 +729,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -653,13 +743,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -667,13 +757,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -681,13 +771,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -695,13 +785,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -709,13 +799,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -723,13 +813,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -737,13 +827,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -751,13 +841,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -765,13 +855,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -779,13 +869,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -793,13 +883,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -807,13 +897,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -821,13 +911,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -835,13 +925,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -849,13 +939,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -863,13 +953,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -877,13 +967,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -891,13 +981,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -905,13 +995,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -919,13 +1009,13 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -933,13 +1023,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -947,13 +1037,13 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -961,13 +1051,13 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -975,13 +1065,13 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -989,13 +1079,13 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1003,13 +1093,13 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1017,13 +1107,13 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1031,13 +1121,13 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1045,13 +1135,13 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1059,13 +1149,13 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1073,13 +1163,13 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1087,13 +1177,265 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>67</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D43" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" t="s">
+        <v>96</v>
+      </c>
+      <c r="D45" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D53" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D55" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/output/法令更新監視台帳_20260317.xlsx
+++ b/output/法令更新監視台帳_20260317.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="108">
   <si>
     <t>法令名</t>
   </si>
@@ -127,9 +127,21 @@
     <t>エネルギーの使用の合理化及び非化石エネルギーへの転換等に関する法律</t>
   </si>
   <si>
+    <t>エネルギーの使用の合理化及び非化石エネルギーへの転換等に関する法律施行令</t>
+  </si>
+  <si>
+    <t>エネルギーの使用の合理化及び非化石エネルギーへの転換等に関する法律施行規則</t>
+  </si>
+  <si>
     <t>地球温暖化対策の推進に関する法律</t>
   </si>
   <si>
+    <t>地球温暖化対策の推進に関する法律施行令</t>
+  </si>
+  <si>
+    <t>地球温暖化対策の推進に関する法律施行規則</t>
+  </si>
+  <si>
     <t>建築物のエネルギー消費性能の向上等に関する法律</t>
   </si>
   <si>
@@ -142,7 +154,10 @@
     <t>フロン類の使用の合理化及び管理の適正化に関する法律</t>
   </si>
   <si>
-    <t>特定家庭用機器再商品化法</t>
+    <t>フロン類の使用の合理化及び管理の適正化に関する法律施行令</t>
+  </si>
+  <si>
+    <t>フロン類の使用の合理化及び管理の適正化に関する法律施行規則特定家庭用機器再商品化法</t>
   </si>
   <si>
     <t>使用済小型電子機器等の再資源化の促進に関する法律</t>
@@ -253,9 +268,18 @@
     <t>令和四年一二月九日法律第九七号</t>
   </si>
   <si>
+    <t>令和七年三月二七日経済産業省令第一七号</t>
+  </si>
+  <si>
     <t>令和六年六月一九日法律第五六号</t>
   </si>
   <si>
+    <t>令和七年九月一八日政令第三二七号</t>
+  </si>
+  <si>
+    <t>令和六年一〇月二五日環境省令第二六号</t>
+  </si>
+  <si>
     <t>令和六年六月一九日法律第五三号</t>
   </si>
   <si>
@@ -265,7 +289,10 @@
     <t>令和六年一二月二七日国土交通省令第一一一号</t>
   </si>
   <si>
-    <t>平成二九年六月一六日法律第六一号</t>
+    <t>令和元年一二月一三日政令第一八三号</t>
+  </si>
+  <si>
+    <t>取得失敗（名称不一致）</t>
   </si>
   <si>
     <t>（改正法令）附　則</t>
@@ -305,6 +332,9 @@
   </si>
   <si>
     <t>未確認</t>
+  </si>
+  <si>
+    <t>要確認</t>
   </si>
   <si>
     <t>2026-03-17</t>
@@ -665,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -687,13 +717,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -701,13 +731,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -715,13 +745,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -729,13 +759,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -743,13 +773,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -757,13 +787,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -771,13 +801,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -785,13 +815,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -799,13 +829,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -813,13 +843,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -827,13 +857,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -841,13 +871,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -855,13 +885,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -869,13 +899,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -883,13 +913,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -897,13 +927,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -911,13 +941,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -925,13 +955,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -939,13 +969,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -953,13 +983,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -967,13 +997,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -981,13 +1011,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -995,13 +1025,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1009,13 +1039,13 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1023,13 +1053,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1037,13 +1067,13 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1051,13 +1081,13 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1065,13 +1095,13 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1079,13 +1109,13 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1093,13 +1123,13 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1107,13 +1137,13 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1121,13 +1151,13 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1135,13 +1165,13 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1149,13 +1179,13 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1163,13 +1193,13 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1177,13 +1207,13 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1191,13 +1221,13 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1205,13 +1235,13 @@
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1219,13 +1249,13 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1233,13 +1263,13 @@
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1247,13 +1277,13 @@
         <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1261,13 +1291,13 @@
         <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1275,13 +1305,13 @@
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1289,13 +1319,13 @@
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1303,13 +1333,13 @@
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1317,13 +1347,13 @@
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1331,13 +1361,13 @@
         <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1345,13 +1375,13 @@
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1359,13 +1389,13 @@
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C50" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1373,13 +1403,13 @@
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1387,13 +1417,13 @@
         <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1401,13 +1431,13 @@
         <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1415,13 +1445,13 @@
         <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1429,13 +1459,83 @@
         <v>57</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" t="s">
+        <v>105</v>
+      </c>
+      <c r="D56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" t="s">
+        <v>103</v>
+      </c>
+      <c r="C57" t="s">
+        <v>105</v>
+      </c>
+      <c r="D57" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" t="s">
+        <v>105</v>
+      </c>
+      <c r="D59" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" t="s">
+        <v>104</v>
+      </c>
+      <c r="C60" t="s">
+        <v>105</v>
+      </c>
+      <c r="D60" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/output/法令更新監視台帳_20260317.xlsx
+++ b/output/法令更新監視台帳_20260317.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t.namigata\Desktop\python_practice\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CC2F42-FDE4-4694-908F-D3F724275B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -343,12 +349,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -356,8 +362,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -403,17 +416,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -451,7 +472,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -485,6 +506,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -519,9 +541,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -694,11 +717,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D60"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="84.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.5" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -712,7 +741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -726,7 +755,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -740,7 +769,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -754,7 +783,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -768,7 +797,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -782,7 +811,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -796,7 +825,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -810,7 +839,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -824,7 +853,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -838,7 +867,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -852,7 +881,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -866,7 +895,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -880,7 +909,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -894,7 +923,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -908,7 +937,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -922,7 +951,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -936,7 +965,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -950,7 +979,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -964,7 +993,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -978,7 +1007,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -992,7 +1021,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1006,7 +1035,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1049,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1034,7 +1063,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1048,7 +1077,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1062,7 +1091,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1076,7 +1105,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1090,7 +1119,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1104,7 +1133,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -1118,7 +1147,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -1132,7 +1161,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -1146,7 +1175,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -1160,7 +1189,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -1174,7 +1203,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1188,7 +1217,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -1202,7 +1231,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1216,7 +1245,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1230,7 +1259,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1244,7 +1273,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1258,7 +1287,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -1272,7 +1301,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1286,7 +1315,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1300,7 +1329,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1314,7 +1343,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -1328,7 +1357,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -1342,7 +1371,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -1356,7 +1385,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1370,7 +1399,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1384,7 +1413,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -1398,7 +1427,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1412,7 +1441,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -1426,7 +1455,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1440,7 +1469,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -1454,7 +1483,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -1468,7 +1497,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -1482,7 +1511,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -1496,7 +1525,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -1510,7 +1539,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -1524,7 +1553,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -1539,6 +1568,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>